--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_296_R30.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_296_R30.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.602</v>
+        <v>3.9126</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1049</v>
+        <v>5.4155</v>
       </c>
       <c r="F2" t="n">
         <v>-1.5029</v>
@@ -610,10 +610,10 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0104</v>
+        <v>1.321</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3462</v>
+        <v>0.6567</v>
       </c>
       <c r="U2" t="n">
         <v>0.6642</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5138</v>
+        <v>2.0204</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7139</v>
+        <v>3.5553</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2001</v>
+        <v>-1.5349</v>
       </c>
       <c r="G3" t="n">
-        <v>1.4592</v>
+        <v>0.7123</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2651</v>
+        <v>3.978</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1941</v>
+        <v>-3.2657</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2823</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1916</v>
+        <v>4.5576</v>
       </c>
       <c r="L3" t="n">
-        <v>1.0907</v>
+        <v>-1.1077</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8231</v>
+        <v>-2.7377</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9265</v>
+        <v>-0.5796</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8966</v>
+        <v>-2.1581</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5933</v>
+        <v>0.4679</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8259</v>
+        <v>0.1928</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7675</v>
+        <v>0.275</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4665</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5119</v>
+        <v>1.5544</v>
       </c>
       <c r="E4" t="n">
-        <v>1.333</v>
+        <v>3.1241</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1789</v>
+        <v>-1.5697</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4711</v>
+        <v>1.4592</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4309</v>
+        <v>1.2651</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0402</v>
+        <v>0.1941</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2934</v>
+        <v>3.2823</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1462</v>
+        <v>2.1916</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>1.0907</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8223</v>
+        <v>-1.8231</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7153</v>
+        <v>-0.9265</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.107</v>
+        <v>-0.8966</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4145</v>
+        <v>0.6339</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1993</v>
+        <v>0.2361</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2153</v>
+        <v>0.3978</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1418</v>
+        <v>-1.4665</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.238</v>
+        <v>0.8974</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7729</v>
+        <v>-0.3337</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5349</v>
+        <v>1.2311</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7123</v>
+        <v>0.3658</v>
       </c>
       <c r="H5" t="n">
-        <v>3.978</v>
+        <v>0.4227</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.2657</v>
+        <v>-0.0569</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>0.1586</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5576</v>
+        <v>0.3193</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1077</v>
+        <v>-0.1607</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7377</v>
+        <v>0.2071</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5796</v>
+        <v>0.1034</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1581</v>
+        <v>0.1038</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3145</v>
+        <v>-0.5406</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5895</v>
+        <v>-0.4048</v>
       </c>
       <c r="U5" t="n">
-        <v>0.275</v>
+        <v>-0.1357</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6271</v>
+        <v>0.7451</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8284</v>
+        <v>0.9463</v>
       </c>
       <c r="F6" t="n">
         <v>-0.2012</v>
@@ -922,10 +922,10 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3892</v>
+        <v>-0.2713</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6642</v>
+        <v>-0.5463</v>
       </c>
       <c r="U6" t="n">
         <v>0.275</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5778</v>
+        <v>0.3667</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4517</v>
+        <v>0.3894</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0295</v>
+        <v>-0.0227</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3658</v>
+        <v>0.4711</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4227</v>
+        <v>0.4309</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0569</v>
+        <v>0.0402</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1586</v>
+        <v>1.2934</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3193</v>
+        <v>1.1462</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1607</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2071</v>
+        <v>-0.8223</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1034</v>
+        <v>-0.7153</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1038</v>
+        <v>-0.107</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8602</v>
+        <v>0.2693</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5228</v>
+        <v>0.2557</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3374</v>
+        <v>0.0136</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2346</v>
+        <v>0.3446</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2671</v>
+        <v>0.3562</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5017</v>
+        <v>-0.0116</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4621</v>
+        <v>2.0655</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2305</v>
+        <v>0.2822</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6926</v>
+        <v>1.7833</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8373</v>
+        <v>2.8879</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1982</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6391</v>
+        <v>2.0476</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3752</v>
+        <v>-0.8223</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4287</v>
+        <v>-0.5581</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0535</v>
+        <v>-0.2643</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2328</v>
+        <v>0.1346</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5702</v>
+        <v>-0.2122</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3374</v>
+        <v>0.3468</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0751</v>
+        <v>-0.0356</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1203</v>
+        <v>-0.7389</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0452</v>
+        <v>0.7033</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0655</v>
+        <v>-0.4621</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2822</v>
+        <v>0.2305</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7833</v>
+        <v>-0.6926</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8879</v>
+        <v>-0.8373</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8401999999999999</v>
+        <v>-0.1982</v>
       </c>
       <c r="L9" t="n">
-        <v>2.0476</v>
+        <v>-0.6391</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8223</v>
+        <v>0.3752</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5581</v>
+        <v>0.4287</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2643</v>
+        <v>-0.0535</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1349</v>
+        <v>-0.0373</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>0.0984</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3132</v>
+        <v>-0.1357</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3491</v>
+        <v>-0.8122</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4049</v>
+        <v>-1.3302</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0558</v>
+        <v>0.5181</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5878</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0763</v>
+        <v>0.6133</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0395</v>
+        <v>0.1142</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0368</v>
+        <v>0.4991</v>
       </c>
       <c r="V10" t="n">
         <v>0.3943</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2325</v>
+        <v>-1.7538</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6123</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8448</v>
+        <v>-2.6768</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8242</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1278</v>
+        <v>0.6065</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0351</v>
+        <v>0.2754</v>
       </c>
       <c r="U11" t="n">
-        <v>0.163</v>
+        <v>0.331</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6149</v>
+        <v>-2.0355</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3386</v>
+        <v>-1.028</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2763</v>
+        <v>-1.0074</v>
       </c>
       <c r="G12" t="n">
         <v>-1.341</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5755</v>
+        <v>0.004</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1019</v>
+        <v>0.2087</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4736</v>
+        <v>-0.2047</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9304</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8794</v>
+        <v>-2.5262</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6744</v>
+        <v>-1.5565</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2049</v>
+        <v>-0.9697</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9853</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3378</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1845</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5223</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.0722</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3044</v>
+        <v>2.6779</v>
       </c>
       <c r="E14" t="n">
-        <v>9.349</v>
+        <v>9.7224</v>
       </c>
       <c r="F14" t="n">
         <v>-7.0444</v>
@@ -1546,13 +1546,13 @@
         <v>10.438</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5186</v>
+        <v>3.8923</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4349999999999998</v>
+        <v>0.8080999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.083899999999999</v>
+        <v>3.084</v>
       </c>
       <c r="V14" t="n">
         <v>0.6779000000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8839</v>
+        <v>3.6379</v>
       </c>
       <c r="E15" t="n">
-        <v>5.673</v>
+        <v>3.2399</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7892</v>
+        <v>0.3979</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6784</v>
+        <v>3.5523</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1202</v>
+        <v>-0.5666</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4418</v>
+        <v>4.1189</v>
       </c>
       <c r="J15" t="n">
-        <v>2.06</v>
+        <v>3.6957</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1399</v>
+        <v>-0.4265</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9201</v>
+        <v>4.1222</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7384</v>
+        <v>-0.1434</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.2601</v>
+        <v>-0.1401</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4783</v>
+        <v>-0.0033</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6499</v>
+        <v>-0.002</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9505</v>
+        <v>-0.4558</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6994</v>
+        <v>0.4538</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8223</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3533</v>
+        <v>3.2417</v>
       </c>
       <c r="E16" t="n">
         <v>3.1051</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2482</v>
+        <v>0.1366</v>
       </c>
       <c r="G16" t="n">
         <v>1.1078</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1037</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1845</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2882</v>
+        <v>0.1766</v>
       </c>
       <c r="V16" t="n">
         <v>1.214</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6892</v>
+        <v>2.8965</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6502</v>
+        <v>4.0217</v>
       </c>
       <c r="F17" t="n">
-        <v>0.039</v>
+        <v>-1.1252</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5523</v>
+        <v>-0.6784</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5666</v>
+        <v>-1.1202</v>
       </c>
       <c r="I17" t="n">
-        <v>4.1189</v>
+        <v>0.4418</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6957</v>
+        <v>2.06</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4265</v>
+        <v>1.1399</v>
       </c>
       <c r="L17" t="n">
-        <v>4.1222</v>
+        <v>0.9201</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1434</v>
+        <v>-2.7384</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1401</v>
+        <v>-2.2601</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0033</v>
+        <v>-0.4783</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9506</v>
+        <v>0.6625</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0455</v>
+        <v>0.2992</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0949</v>
+        <v>0.3633</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4336</v>
+        <v>1.523</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4381</v>
+        <v>3.2022</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0045</v>
+        <v>-1.6792</v>
       </c>
       <c r="G18" t="n">
         <v>2.7053</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8079</v>
+        <v>-0.7185</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1098</v>
+        <v>-0.3457</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.698</v>
+        <v>-0.3727</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1488</v>
+        <v>0.2551</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7777</v>
+        <v>2.0136</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9265</v>
+        <v>-1.7585</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1194</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.3213</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2025</v>
+        <v>-0.0345</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9207</v>
+        <v>-0.5167</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4132</v>
+        <v>-0.1773</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5074</v>
+        <v>-0.3394</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4941</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6585</v>
+        <v>-0.2546</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2851</v>
+        <v>-0.1171</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1696</v>
+        <v>-1.9337</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2104</v>
+        <v>0.4463</v>
       </c>
       <c r="F21" t="n">
         <v>-2.3801</v>
@@ -2092,10 +2092,10 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6212</v>
+        <v>-0.3853</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U21" t="n">
         <v>-0.0984</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9592</v>
+        <v>-2.2014</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5834</v>
+        <v>-1.9937</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3758</v>
+        <v>-0.2078</v>
       </c>
       <c r="G22" t="n">
         <v>1.2536</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7515</v>
+        <v>-0.9937</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2696</v>
+        <v>-0.6798</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4819</v>
+        <v>-0.3139</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.457</v>
+        <v>-3.8724</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5806</v>
+        <v>-4.0525</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1236</v>
+        <v>0.1801</v>
       </c>
       <c r="G23" t="n">
         <v>0.0974</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3888</v>
+        <v>-0.0266</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2636</v>
+        <v>-0.2082</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1252</v>
+        <v>0.1817</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.009</v>
+        <v>-4.548</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2328</v>
+        <v>-2.761</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7762</v>
+        <v>-1.787</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7365</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1461</v>
+        <v>-0.6851</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2696</v>
+        <v>-0.7978</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1235</v>
+        <v>0.1127</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7501</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3043</v>
+        <v>-1.518</v>
       </c>
       <c r="E25" t="n">
-        <v>7.0445</v>
+        <v>7.044300000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.3489</v>
+        <v>-8.5626</v>
       </c>
       <c r="G25" t="n">
-        <v>3.052000000000001</v>
+        <v>3.052</v>
       </c>
       <c r="H25" t="n">
         <v>-7.454400000000001</v>
@@ -2404,13 +2404,13 @@
         <v>9.2784</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.5187</v>
+        <v>-2.7325</v>
       </c>
       <c r="T25" t="n">
         <v>-3.0839</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4347</v>
+        <v>0.3514999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6779000000000002</v>
